--- a/translations/welsh-translations/xlsx/02a-cookies.xlsx
+++ b/translations/welsh-translations/xlsx/02a-cookies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
   <si>
     <t>Translator notes</t>
   </si>
@@ -110,6 +110,12 @@
   </si>
   <si>
     <t>Maintains your authenticated server-side session</t>
+  </si>
+  <si>
+    <t>cookies.csrf.purpose</t>
+  </si>
+  <si>
+    <t>Prevents unauthorised requests being submitted while you use this service</t>
   </si>
   <si>
     <t>cookies.oauthState.purpose</t>
@@ -520,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -831,8 +837,28 @@
         <v>13</v>
       </c>
     </row>
+    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:F18"/>
+  <autoFilter ref="A5:F19"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>

--- a/translations/welsh-translations/xlsx/02a-cookies.xlsx
+++ b/translations/welsh-translations/xlsx/02a-cookies.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BC52B-A66A-4D5C-A6BB-B003A05CA92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
+    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
   <si>
     <t>Translator notes</t>
   </si>
@@ -37,9 +41,6 @@
     <t>Welsh</t>
   </si>
   <si>
-    <t>Figma link</t>
-  </si>
-  <si>
     <t>cookies.pageTitle</t>
   </si>
   <si>
@@ -128,27 +129,77 @@
   </si>
   <si>
     <t>When you close your browser</t>
+  </si>
+  <si>
+    <t>Figma link for this content</t>
+  </si>
+  <si>
+    <t>There is no Figma link for this content</t>
+  </si>
+  <si>
+    <t>Cwcis</t>
+  </si>
+  <si>
+    <t>Mae cwcis yn ffeiliau bach sy’n cael eu cadw ar eich ffôn, eich tabled neu eich cyfrifiadur pan fyddwch chi’n ymweld â gwefan.</t>
+  </si>
+  <si>
+    <t>Cwcis hanfodol</t>
+  </si>
+  <si>
+    <t>Mae cwcis hanfodol yn cadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn. Does dim angen i ni ofyn am ganiatâd i’w defnyddio.</t>
+  </si>
+  <si>
+    <t>Enw</t>
+  </si>
+  <si>
+    <t>Pwrpas</t>
+  </si>
+  <si>
+    <t>Yn dod i ben</t>
+  </si>
+  <si>
+    <t>Cwcis hanfodol rydym yn eu defnyddio</t>
+  </si>
+  <si>
+    <t>Yn cynnal eich sesiwn ochr gweinydd wedi’i dilysu</t>
+  </si>
+  <si>
+    <t>Yn atal cyflwyno ceisiadau heb awdurdod wrth i chi ddefnyddio’r gwasanaeth hwn</t>
+  </si>
+  <si>
+    <t>Cwci cyflwr OAuth dros dro sy’n cael ei ddefnyddio yn ystod llif ailgyfeirio mewngofnodi Azure AD B2C</t>
+  </si>
+  <si>
+    <t>Pan fyddwch chi’n cau eich porwr</t>
+  </si>
+  <si>
+    <t>Rydym yn defnyddio cwcis i storio eich sesiwn mewngofnodi ac i gadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -176,15 +227,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,9 +582,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -535,336 +592,336 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>13</v>
+      <c r="E19" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F19"/>
+  <autoFilter ref="A5:F19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/translations/welsh-translations/xlsx/02a-cookies.xlsx
+++ b/translations/welsh-translations/xlsx/02a-cookies.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BC52B-A66A-4D5C-A6BB-B003A05CA92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="52">
   <si>
     <t>Translator notes</t>
   </si>
@@ -41,6 +37,9 @@
     <t>Welsh</t>
   </si>
   <si>
+    <t>Figma link</t>
+  </si>
+  <si>
     <t>cookies.pageTitle</t>
   </si>
   <si>
@@ -53,6 +52,9 @@
     <t>Cookies</t>
   </si>
   <si>
+    <t>Cwcis</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,141 +67,127 @@
     <t>Cookies are small files saved on your phone, tablet or computer when you visit a website.</t>
   </si>
   <si>
+    <t>Mae cwcis yn ffeiliau bach sy’n cael eu cadw ar eich ffôn, eich tabled neu eich cyfrifiadur pan fyddwch chi’n ymweld â gwefan.</t>
+  </si>
+  <si>
     <t>cookies.introParagraph2</t>
   </si>
   <si>
     <t>We use cookies to store your sign-in session and keep your information secure while you use this service.</t>
   </si>
   <si>
+    <t>Rydym yn defnyddio cwcis i storio eich sesiwn mewngofnodi ac i gadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn.</t>
+  </si>
+  <si>
     <t>cookies.essentialCookiesHeading</t>
   </si>
   <si>
     <t>Essential cookies</t>
   </si>
   <si>
+    <t>Cwcis hanfodol</t>
+  </si>
+  <si>
     <t>cookies.essentialCookiesDescription</t>
   </si>
   <si>
     <t>Essential cookies keep your information secure while you use this service. We do not need to ask permission to use them.</t>
   </si>
   <si>
+    <t>Mae cwcis hanfodol yn cadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn. Does dim angen i ni ofyn am ganiatâd i’w defnyddio.</t>
+  </si>
+  <si>
     <t>cookies.table.name</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Enw</t>
+  </si>
+  <si>
     <t>cookies.table.purpose</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
+    <t>Pwrpas</t>
+  </si>
+  <si>
     <t>cookies.table.expires</t>
   </si>
   <si>
     <t>Expires</t>
   </si>
   <si>
+    <t>Yn dod i ben</t>
+  </si>
+  <si>
     <t>cookies.table.essentialCookiesWeUse</t>
   </si>
   <si>
     <t>Essential cookies we use</t>
   </si>
   <si>
+    <t>Cwcis hanfodol rydym yn eu defnyddio</t>
+  </si>
+  <si>
     <t>cookies.session.purpose</t>
   </si>
   <si>
     <t>Maintains your authenticated server-side session</t>
   </si>
   <si>
+    <t>Yn cynnal eich sesiwn ochr gweinydd wedi’i dilysu</t>
+  </si>
+  <si>
     <t>cookies.csrf.purpose</t>
   </si>
   <si>
     <t>Prevents unauthorised requests being submitted while you use this service</t>
   </si>
   <si>
+    <t>Yn atal cyflwyno ceisiadau heb awdurdod wrth i chi ddefnyddio’r gwasanaeth hwn</t>
+  </si>
+  <si>
     <t>cookies.oauthState.purpose</t>
   </si>
   <si>
     <t>Temporary OAuth state cookie used during the Azure AD B2C login redirect flow</t>
   </si>
   <si>
+    <t>Cwci cyflwr OAuth dros dro sy’n cael ei ddefnyddio yn ystod llif ailgyfeirio mewngofnodi Azure AD B2C</t>
+  </si>
+  <si>
     <t>cookies.oauthState.expires</t>
   </si>
   <si>
     <t>When you close your browser</t>
   </si>
   <si>
-    <t>Figma link for this content</t>
-  </si>
-  <si>
-    <t>There is no Figma link for this content</t>
-  </si>
-  <si>
-    <t>Cwcis</t>
-  </si>
-  <si>
-    <t>Mae cwcis yn ffeiliau bach sy’n cael eu cadw ar eich ffôn, eich tabled neu eich cyfrifiadur pan fyddwch chi’n ymweld â gwefan.</t>
-  </si>
-  <si>
-    <t>Cwcis hanfodol</t>
-  </si>
-  <si>
-    <t>Mae cwcis hanfodol yn cadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn. Does dim angen i ni ofyn am ganiatâd i’w defnyddio.</t>
-  </si>
-  <si>
-    <t>Enw</t>
-  </si>
-  <si>
-    <t>Pwrpas</t>
-  </si>
-  <si>
-    <t>Yn dod i ben</t>
-  </si>
-  <si>
-    <t>Cwcis hanfodol rydym yn eu defnyddio</t>
-  </si>
-  <si>
-    <t>Yn cynnal eich sesiwn ochr gweinydd wedi’i dilysu</t>
-  </si>
-  <si>
-    <t>Yn atal cyflwyno ceisiadau heb awdurdod wrth i chi ddefnyddio’r gwasanaeth hwn</t>
-  </si>
-  <si>
-    <t>Cwci cyflwr OAuth dros dro sy’n cael ei ddefnyddio yn ystod llif ailgyfeirio mewngofnodi Azure AD B2C</t>
-  </si>
-  <si>
     <t>Pan fyddwch chi’n cau eich porwr</t>
-  </si>
-  <si>
-    <t>Rydym yn defnyddio cwcis i storio eich sesiwn mewngofnodi ac i gadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -227,21 +215,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,9 +564,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -592,336 +574,336 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="4" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:F19"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/translations/welsh-translations/xlsx/02a-cookies.xlsx
+++ b/translations/welsh-translations/xlsx/02a-cookies.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BC52B-A66A-4D5C-A6BB-B003A05CA92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="52">
   <si>
     <t>Translator notes</t>
   </si>
@@ -41,6 +37,9 @@
     <t>Welsh</t>
   </si>
   <si>
+    <t>Figma link</t>
+  </si>
+  <si>
     <t>cookies.pageTitle</t>
   </si>
   <si>
@@ -53,6 +52,9 @@
     <t>Cookies</t>
   </si>
   <si>
+    <t>Cwcis</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,46 +67,70 @@
     <t>Cookies are small files saved on your phone, tablet or computer when you visit a website.</t>
   </si>
   <si>
+    <t>Mae cwcis yn ffeiliau bach sy’n cael eu cadw ar eich ffôn, eich tabled neu eich cyfrifiadur pan fyddwch chi’n ymweld â gwefan.</t>
+  </si>
+  <si>
     <t>cookies.introParagraph2</t>
   </si>
   <si>
     <t>We use cookies to store your sign-in session and keep your information secure while you use this service.</t>
   </si>
   <si>
+    <t>Rydym yn defnyddio cwcis i storio eich sesiwn mewngofnodi ac i gadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn.</t>
+  </si>
+  <si>
     <t>cookies.essentialCookiesHeading</t>
   </si>
   <si>
     <t>Essential cookies</t>
   </si>
   <si>
+    <t>Cwcis hanfodol</t>
+  </si>
+  <si>
     <t>cookies.essentialCookiesDescription</t>
   </si>
   <si>
     <t>Essential cookies keep your information secure while you use this service. We do not need to ask permission to use them.</t>
   </si>
   <si>
+    <t>Mae cwcis hanfodol yn cadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn. Does dim angen i ni ofyn am ganiatâd i’w defnyddio.</t>
+  </si>
+  <si>
+    <t>cookies.table.essentialCookiesWeUse</t>
+  </si>
+  <si>
+    <t>Essential cookies we use</t>
+  </si>
+  <si>
+    <t>Cwcis hanfodol rydym yn eu defnyddio</t>
+  </si>
+  <si>
     <t>cookies.table.name</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Enw</t>
+  </si>
+  <si>
     <t>cookies.table.purpose</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
+    <t>Pwrpas</t>
+  </si>
+  <si>
     <t>cookies.table.expires</t>
   </si>
   <si>
     <t>Expires</t>
   </si>
   <si>
-    <t>cookies.table.essentialCookiesWeUse</t>
-  </si>
-  <si>
-    <t>Essential cookies we use</t>
+    <t>Yn dod i ben</t>
   </si>
   <si>
     <t>cookies.session.purpose</t>
@@ -113,93 +139,55 @@
     <t>Maintains your authenticated server-side session</t>
   </si>
   <si>
+    <t>Yn cynnal eich sesiwn ochr gweinydd wedi’i dilysu</t>
+  </si>
+  <si>
     <t>cookies.csrf.purpose</t>
   </si>
   <si>
     <t>Prevents unauthorised requests being submitted while you use this service</t>
   </si>
   <si>
+    <t>Yn atal cyflwyno ceisiadau heb awdurdod wrth i chi ddefnyddio’r gwasanaeth hwn</t>
+  </si>
+  <si>
     <t>cookies.oauthState.purpose</t>
   </si>
   <si>
     <t>Temporary OAuth state cookie used during the Azure AD B2C login redirect flow</t>
   </si>
   <si>
+    <t>Cwci cyflwr OAuth dros dro sy’n cael ei ddefnyddio yn ystod llif ailgyfeirio mewngofnodi Azure AD B2C</t>
+  </si>
+  <si>
     <t>cookies.oauthState.expires</t>
   </si>
   <si>
     <t>When you close your browser</t>
   </si>
   <si>
-    <t>Figma link for this content</t>
-  </si>
-  <si>
-    <t>There is no Figma link for this content</t>
-  </si>
-  <si>
-    <t>Cwcis</t>
-  </si>
-  <si>
-    <t>Mae cwcis yn ffeiliau bach sy’n cael eu cadw ar eich ffôn, eich tabled neu eich cyfrifiadur pan fyddwch chi’n ymweld â gwefan.</t>
-  </si>
-  <si>
-    <t>Cwcis hanfodol</t>
-  </si>
-  <si>
-    <t>Mae cwcis hanfodol yn cadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn. Does dim angen i ni ofyn am ganiatâd i’w defnyddio.</t>
-  </si>
-  <si>
-    <t>Enw</t>
-  </si>
-  <si>
-    <t>Pwrpas</t>
-  </si>
-  <si>
-    <t>Yn dod i ben</t>
-  </si>
-  <si>
-    <t>Cwcis hanfodol rydym yn eu defnyddio</t>
-  </si>
-  <si>
-    <t>Yn cynnal eich sesiwn ochr gweinydd wedi’i dilysu</t>
-  </si>
-  <si>
-    <t>Yn atal cyflwyno ceisiadau heb awdurdod wrth i chi ddefnyddio’r gwasanaeth hwn</t>
-  </si>
-  <si>
-    <t>Cwci cyflwr OAuth dros dro sy’n cael ei ddefnyddio yn ystod llif ailgyfeirio mewngofnodi Azure AD B2C</t>
-  </si>
-  <si>
     <t>Pan fyddwch chi’n cau eich porwr</t>
-  </si>
-  <si>
-    <t>Rydym yn defnyddio cwcis i storio eich sesiwn mewngofnodi ac i gadw eich gwybodaeth yn ddiogel wrth i chi ddefnyddio’r gwasanaeth hwn.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -227,21 +215,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,9 +564,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -592,336 +574,336 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="4" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:F19"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>